--- a/data/file_generation/reference/data_73/清洗表_res.xlsx
+++ b/data/file_generation/reference/data_73/清洗表_res.xlsx
@@ -1876,26 +1876,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE81185B-E49E-44AF-8AA5-2BA93BFFA7AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C02EC658-2286-4949-8289-914327301C75}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6A425D3-ED0A-43E3-9F69-68F741CE68A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE6150F2-51D3-4053-9384-1A5EFC992C83}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E036D98-4715-4EB7-AA69-89DF3C8E3B71}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{369EE0E1-8F97-4D2D-A459-A903BB30064B}"/>
 </file>